--- a/oscars.xlsx
+++ b/oscars.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/pythonProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7A7289-0B97-4340-B84D-FD57AB3EFC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D573E46B-4786-6B47-AD38-291983452950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{64EB950D-3CEB-BD46-BBB5-B2892C484FA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -411,7 +411,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -436,6 +436,22 @@
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -473,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -483,6 +499,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,30 +841,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5F2EA9-9154-AC42-A9E3-4350B0A42173}">
   <dimension ref="A1:D97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +878,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -870,7 +892,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -884,7 +906,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -898,7 +920,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -912,7 +934,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -926,7 +948,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -940,7 +962,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -954,7 +976,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -968,7 +990,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,7 +1004,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -996,7 +1018,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1010,7 +1032,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,7 +1046,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1038,7 +1060,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1052,7 +1074,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,7 +1088,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1080,7 +1102,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,7 +1116,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1108,7 +1130,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1122,7 +1144,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1136,7 +1158,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1150,7 +1172,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -1164,7 +1186,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -1172,7 +1194,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -1180,7 +1202,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1188,7 +1210,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -1196,7 +1218,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1204,7 +1226,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -1212,7 +1234,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -1220,7 +1242,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -1228,7 +1250,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -1236,7 +1258,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -1244,7 +1266,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -1252,7 +1274,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -1260,7 +1282,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -1268,7 +1290,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -1276,7 +1298,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -1284,7 +1306,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -1292,7 +1314,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -1300,7 +1322,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -1308,7 +1330,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -1316,7 +1338,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -1324,7 +1346,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -1332,7 +1354,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -1340,7 +1362,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -1348,7 +1370,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -1356,7 +1378,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -1364,7 +1386,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -1372,7 +1394,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -1380,7 +1402,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -1388,7 +1410,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -1396,7 +1418,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -1404,7 +1426,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -1412,7 +1434,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
@@ -1420,7 +1442,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
@@ -1428,7 +1450,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
@@ -1436,7 +1458,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -1444,7 +1466,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -1452,7 +1474,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -1460,7 +1482,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -1468,7 +1490,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -1476,7 +1498,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
@@ -1484,7 +1506,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -1492,7 +1514,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -1500,7 +1522,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -1508,7 +1530,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -1516,7 +1538,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -1524,7 +1546,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -1532,7 +1554,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
@@ -1540,7 +1562,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
@@ -1548,7 +1570,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -1556,7 +1578,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
@@ -1564,7 +1586,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
@@ -1572,7 +1594,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
@@ -1580,7 +1602,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -1588,7 +1610,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
@@ -1596,7 +1618,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -1604,7 +1626,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
@@ -1612,7 +1634,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
@@ -1620,7 +1642,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
@@ -1628,7 +1650,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
@@ -1636,7 +1658,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
@@ -1644,7 +1666,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
@@ -1652,7 +1674,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
@@ -1660,7 +1682,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
@@ -1668,7 +1690,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
@@ -1676,7 +1698,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
@@ -1684,7 +1706,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
@@ -1692,7 +1714,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
@@ -1700,7 +1722,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
@@ -1708,7 +1730,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
@@ -1716,7 +1738,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -1724,7 +1746,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -1732,7 +1754,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -1740,7 +1762,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>

--- a/oscars.xlsx
+++ b/oscars.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D573E46B-4786-6B47-AD38-291983452950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC204758-A81C-1541-BDFE-7141716C1114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{64EB950D-3CEB-BD46-BBB5-B2892C484FA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>Wings</t>
   </si>
@@ -405,6 +405,42 @@
   </si>
   <si>
     <t>Best Animated Feature Year</t>
+  </si>
+  <si>
+    <t>Best Picture Nominated Name</t>
+  </si>
+  <si>
+    <t>Best Picture Nominated Year</t>
+  </si>
+  <si>
+    <t>Anora</t>
+  </si>
+  <si>
+    <t>The Brutalist</t>
+  </si>
+  <si>
+    <t>A Complete Unknown</t>
+  </si>
+  <si>
+    <t>Conclave</t>
+  </si>
+  <si>
+    <t>Dune: Part Two</t>
+  </si>
+  <si>
+    <t>Emilia Pérez</t>
+  </si>
+  <si>
+    <t>Nickel Boys</t>
+  </si>
+  <si>
+    <t>I'm Still Here</t>
+  </si>
+  <si>
+    <t>The Substance</t>
+  </si>
+  <si>
+    <t>Wicked</t>
   </si>
 </sst>
 </file>
@@ -426,18 +462,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="14"/>
@@ -449,6 +473,18 @@
       <b/>
       <u/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
@@ -489,22 +525,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -840,935 +882,1149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5F2EA9-9154-AC42-A9E3-4350B0A42173}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="5">
         <v>1927</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>2001</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="5">
         <v>1929</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>2001</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="5">
         <v>1930</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>2003</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="5">
         <v>1931</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>2004</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="5">
         <v>1932</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>2005</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="5">
         <v>1933</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>2006</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="E7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="5">
         <v>1934</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>2007</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="5">
         <v>1935</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>2008</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="E9" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="5">
         <v>1936</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>2009</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="5">
         <v>1937</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="5">
         <v>2010</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="5">
         <v>1938</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="5">
         <v>2011</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="5">
         <v>1939</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="5">
         <v>2012</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="5">
         <v>1940</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="5">
         <v>2013</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="5">
         <v>1941</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="5">
         <v>2014</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="5">
         <v>1942</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="5">
         <v>2015</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="5">
         <v>1942</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="5">
         <v>2016</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="5">
         <v>1944</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="5">
         <v>2017</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="5">
         <v>1945</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="5">
         <v>2018</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="5">
         <v>1946</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="5">
         <v>2019</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="5">
         <v>1947</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="5">
         <v>2020</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="5">
         <v>1948</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="5">
         <v>2021</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="5">
         <v>1949</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="5">
         <v>2022</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="5">
         <v>1950</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="5">
         <v>2023</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="5">
         <v>1951</v>
       </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="5">
         <v>1952</v>
       </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="5">
         <v>1953</v>
       </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="5">
         <v>1954</v>
       </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="5">
         <v>1955</v>
       </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="5">
         <v>1956</v>
       </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="5">
         <v>1957</v>
       </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="5">
         <v>1958</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="5">
         <v>1959</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="5">
         <v>1960</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="5">
         <v>1961</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="5">
         <v>1962</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="5">
         <v>1963</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="5">
         <v>1964</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="5">
         <v>1965</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="5">
         <v>1966</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="5">
         <v>1967</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="5">
         <v>1968</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="5">
         <v>1969</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="5">
         <v>1970</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="5">
         <v>1971</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="5">
         <v>1972</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="5">
         <v>1973</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="5">
         <v>1974</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="5">
         <v>1975</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="5">
         <v>1976</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="5">
         <v>1977</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="5">
         <v>1978</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="5">
         <v>1979</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="5">
         <v>1980</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="5">
         <v>1981</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="5">
         <v>1982</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="5">
         <v>1983</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="5">
         <v>1984</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="5">
         <v>1985</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="5">
         <v>1986</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="5">
         <v>1987</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="5">
         <v>1988</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+    </row>
+    <row r="63" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="5">
         <v>1989</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="5">
         <v>1990</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="5">
         <v>1991</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="5">
         <v>1992</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="5">
         <v>1993</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="5">
         <v>1994</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="5">
         <v>1995</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="5">
         <v>1996</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="5">
         <v>1997</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="5">
         <v>1998</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="5">
         <v>1999</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="5">
         <v>2000</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="5">
         <v>2001</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="5">
         <v>2002</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="5">
         <v>2003</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="5">
         <v>2004</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="5">
         <v>2004</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="5">
         <v>2006</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="5">
         <v>2007</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="5">
         <v>2008</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="5">
         <v>2008</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+    </row>
+    <row r="84" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="5">
         <v>2010</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="5">
         <v>2011</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="5">
         <v>2012</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="5">
         <v>2013</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="5">
         <v>2014</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="5">
         <v>2015</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+    </row>
+    <row r="90" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="5">
         <v>2016</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+    </row>
+    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="5">
         <v>2017</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="5">
         <v>2018</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+    </row>
+    <row r="93" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="5">
         <v>2019</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="5">
         <v>2021</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+    </row>
+    <row r="96" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="5">
         <v>2022</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="5">
         <v>2023</v>
       </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
